--- a/output/pdf_financials_xlsx/HLU.xlsx
+++ b/output/pdf_financials_xlsx/HLU.xlsx
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.119614</v>
       </c>
     </row>
     <row r="93">
@@ -2586,7 +2586,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HLU.xlsx
+++ b/output/pdf_financials_xlsx/HLU.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.152341</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
         <v>-1.084006</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-15.352084</v>
+        <v>-15.504425</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         <v>-1.084006</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-15.352084</v>
+        <v>-15.504425</v>
       </c>
     </row>
     <row r="30">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/output/pdf_financials_xlsx/HLU.xlsx
+++ b/output/pdf_financials_xlsx/HLU.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.198763</v>
+        <v>0.294013</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.281941</v>
+        <v>0.377191</v>
       </c>
     </row>
     <row r="11">
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.07319199999999999</v>
       </c>
     </row>
     <row r="102">
@@ -1820,7 +1820,7 @@
         <v>0.242772</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-1.7718</v>
+        <v>-1.844992</v>
       </c>
     </row>
     <row r="107">
@@ -2894,7 +2894,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -3410,7 +3414,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
